--- a/data/trans_camb/P1803_2016_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1803_2016_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,97</t>
+          <t>-0,36; 4,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,26</t>
+          <t>2,83; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,32</t>
+          <t>2,05; 5,29</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137,8%</t>
+          <t>138,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 173,24</t>
+          <t>-8,58; 162,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,63; 290,55</t>
+          <t>59,08; 295,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,88; 185,05</t>
+          <t>44,04; 173,55</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21,93</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 60,01</t>
+          <t>0,4; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,37</t>
+          <t>2,04; 6,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 40,47</t>
+          <t>1,8; 4,97</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>515,16%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>312,42%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,44; 1639,08</t>
+          <t>7,38; 150,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 172,77</t>
+          <t>34,08; 161,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,23; 1057,74</t>
+          <t>34,59; 127,83</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,5</t>
+          <t>1,05; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,92</t>
+          <t>2,41; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,19</t>
+          <t>2,3; 5,65</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>106,2%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,48; 243,31</t>
+          <t>18,92; 224,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 136,2</t>
+          <t>36,19; 187,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 142,24</t>
+          <t>41,52; 160,72</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,64</t>
+          <t>2,4; 7,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,41</t>
+          <t>1,71; 6,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,56</t>
+          <t>2,91; 6,44</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,15; 162,25</t>
+          <t>29,87; 151,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 95,86</t>
+          <t>16,86; 97,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,28; 101,87</t>
+          <t>36,37; 102,68</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,72</t>
+          <t>2,24; 4,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,25</t>
+          <t>3,26; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 18,48</t>
+          <t>3,07; 4,74</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>224,6%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138,74%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>73,46; 708,35</t>
+          <t>44,5; 115,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35,32; 104,21</t>
+          <t>54,76; 113,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68,95; 388,12</t>
+          <t>55,54; 100,64</t>
         </is>
       </c>
     </row>
